--- a/docs/Logic Requirements/Ageipelago El Cid.xlsx
+++ b/docs/Logic Requirements/Ageipelago El Cid.xlsx
@@ -5,15 +5,21 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/BB6DD295C338E39F/Desktop/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\stefb\OneDrive\Desktop\Logic Requirements\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="53" documentId="8_{8A0A14B8-1491-4145-A422-5832A82E26A8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{570C51EE-A6FD-493B-85A2-6B3E8E985559}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D1B10145-77F0-44B5-BB7A-537F49BA6BCB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28545" yWindow="1335" windowWidth="27045" windowHeight="13740" xr2:uid="{B8266A09-EF6B-4D9A-952F-8D97365221FC}"/>
+    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="6" xr2:uid="{B8266A09-EF6B-4D9A-952F-8D97365221FC}"/>
   </bookViews>
   <sheets>
-    <sheet name="Tabelle1" sheetId="1" r:id="rId1"/>
+    <sheet name="El Cid" sheetId="1" r:id="rId1"/>
+    <sheet name="Brother against Brother" sheetId="2" r:id="rId2"/>
+    <sheet name="The Enemy of my Enemy" sheetId="3" r:id="rId3"/>
+    <sheet name="The Exile of The Cid" sheetId="4" r:id="rId4"/>
+    <sheet name="Black Guards" sheetId="5" r:id="rId5"/>
+    <sheet name="King of Valencia" sheetId="6" r:id="rId6"/>
+    <sheet name="Reconquista" sheetId="7" r:id="rId7"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -37,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="80" uniqueCount="80">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="588" uniqueCount="190">
   <si>
     <t>Scenario</t>
   </si>
@@ -2186,182 +2192,6 @@
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
-      <t>Moderate:</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="14"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">
-Starting Army:
-3 Light Cavalry
-8 Knights
-4 Conquistdores
-4 Long Swordsmen
-10 Pikemen
-10 Archers
-4 Mangonels
-1 Missionary
-Later:
-5 Knights
-12 Long Swordsmen
-2 Missionaries
-Endless Scorpions
-1 Battering Ram
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="14"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Standard:</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="14"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">
-Starting Army:
-Identical to Moderate
-Later:
-1 Missionary
-1 Battering Ram
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="14"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Hard:</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="14"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">
-Starting Army is identical to Moderate
-Later:
-5 Knights
-12 Long Swordsmen
-4 Missionaries
-Endless Scorpions
-3 Battering Rams</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="14"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">Moderate:
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="14"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">Starting Army:
- 6 Chevalier
-1 Monk
-Later:
-7 Knights
-10 Long Swordsmen
-2 Monks
-5 Battering Rams
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="14"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Standard:</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="14"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">
-Starting Army:
-Identical to Moderate
-Later:
-5 Knights
-5 Battering Rams
-1 Monk
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="14"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Hard:</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="14"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">
-Identical to Moderate</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="14"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
       <t xml:space="preserve">Moderate:
 </t>
     </r>
@@ -2628,93 +2458,6 @@
       </rPr>
       <t xml:space="preserve">
 Starting Army:
-19 Camel Riders
-5 Mamelukes
-8 Camel Archers
-5 Onagers
-Later:
-5 Hussars
-6 Heavy Camel Riders
-10 Heavy Cavalry Archers
-10 Camel Archers
-2 Trebuchets
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="14"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Standard:</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="14"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">
-Starting Army:
-10 Camel Riders
-4 Mamelukes
-6 Camel Archers
-0 Onagers
-Later:
-6 Heavy Camel Riders
-2 Trebuchets
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="14"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Hard:</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="14"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">
-Identical to Moderate</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="14"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Moderate:</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="14"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">
-Starting Army:
 4 Knights
 6 Camel Riders
 4 Cavalry Archers
@@ -2773,92 +2516,6 @@
       </rPr>
       <t xml:space="preserve">
 Identical to Moderate</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="14"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Moderate:</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="14"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">
-10 Pikemen
-10 Elite Skirmishers
-6 Heavy Camel Riders
-3 Scorpions
-2 Trebuchets
-4 Galleons
-3 Heavy Demolition Ships
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="14"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Standard:</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="14"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">
-5 Pikemen
-6 Heavy Camel Riders
-2 Trebuchets
-3 Heavy Demolition Ships
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="14"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Hard:</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="14"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">
-10 Pikemen
-10 Elite Skirmishers
-6 Heavy Camel Riders
-3 Scorpions
-2 Trebuchets
-2 Monks
-4 Galleons
-3 Heavy Demolition Ships</t>
     </r>
   </si>
   <si>
@@ -3226,107 +2883,6 @@
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve">
-Starting Army:
-3 Galleons
-Later:
-4 Fast Fire Ships
-8 Galleons
-2 Elite Cannon Galleons
-10 Heavy Cavalry Archers
-2 Elite Genitour
-6 Heavy Camel Riders
-5 Hussars
-4 Capped Rams
-1 Monk
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="14"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Standard:</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="14"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">
-Starting Army:
-Identical to Moderate
-Later:
-4 Fast Fire Ships
-2 Galleons
-10 Heavy Cavalry Archers
-2 Elite Genitour
-6 Heavy Camel Riders
-5 Hussars
-4 Capped Rams
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="14"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Hard:</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="14"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">
-Starting Army:
-Identical to Moderate
-Later:
-4 Fast Fire Ships
-8 Galleons
-3 Elite Cannon Galleons
-10 Heavy Cavalry Archers
-2 Elite Genitour
-6 Heavy Camel Riders
-5 Hussars
-4 Capped Rams
-3 Monks</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="14"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Moderate:</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="14"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">
 4 Fast Fire Ships
 8 Galleons
 4 Elite Cannon Galleons
@@ -3400,12 +2956,933 @@
 4 Monks</t>
     </r>
   </si>
+  <si>
+    <t>No items required</t>
+  </si>
+  <si>
+    <t>Champion</t>
+  </si>
+  <si>
+    <t>Two-Handed Swordsman</t>
+  </si>
+  <si>
+    <t>Long Swordsman</t>
+  </si>
+  <si>
+    <t>Elite Skirmisher</t>
+  </si>
+  <si>
+    <t>Requires Transport Ship</t>
+  </si>
+  <si>
+    <t>Requires Dock</t>
+  </si>
+  <si>
+    <t>Galleon</t>
+  </si>
+  <si>
+    <t>Wonder</t>
+  </si>
+  <si>
+    <t>War Galley</t>
+  </si>
+  <si>
+    <t>Dock</t>
+  </si>
+  <si>
+    <t>Watch Tower</t>
+  </si>
+  <si>
+    <t>Outpost</t>
+  </si>
+  <si>
+    <t>Trebuchet</t>
+  </si>
+  <si>
+    <t>Fortified Wall</t>
+  </si>
+  <si>
+    <t>Stone Gate</t>
+  </si>
+  <si>
+    <t>Scorpion</t>
+  </si>
+  <si>
+    <t>Stone Wall</t>
+  </si>
+  <si>
+    <t>Light Cavalry</t>
+  </si>
+  <si>
+    <t>Castle</t>
+  </si>
+  <si>
+    <t>Blacksmith</t>
+  </si>
+  <si>
+    <t>Barracks</t>
+  </si>
+  <si>
+    <t>Siege Ram</t>
+  </si>
+  <si>
+    <t>University</t>
+  </si>
+  <si>
+    <t>Capped Ram</t>
+  </si>
+  <si>
+    <t>Mining Camp</t>
+  </si>
+  <si>
+    <t>Battering Ram</t>
+  </si>
+  <si>
+    <t>Monastery</t>
+  </si>
+  <si>
+    <t>Market</t>
+  </si>
+  <si>
+    <t>Monk</t>
+  </si>
+  <si>
+    <t>Archery Range</t>
+  </si>
+  <si>
+    <t>Mill</t>
+  </si>
+  <si>
+    <t>Scout Cavalry</t>
+  </si>
+  <si>
+    <t>Stable</t>
+  </si>
+  <si>
+    <t>Crossbowman</t>
+  </si>
+  <si>
+    <t>Town Center</t>
+  </si>
+  <si>
+    <t>Villager</t>
+  </si>
+  <si>
+    <t>Lumber Camp</t>
+  </si>
+  <si>
+    <t>Siege Workshop</t>
+  </si>
+  <si>
+    <t>Wild Boar</t>
+  </si>
+  <si>
+    <t>Farm</t>
+  </si>
+  <si>
+    <t>Sheep</t>
+  </si>
+  <si>
+    <t>House</t>
+  </si>
+  <si>
+    <t>Deer</t>
+  </si>
+  <si>
+    <t>Destructible Buildings</t>
+  </si>
+  <si>
+    <t>Killable Units</t>
+  </si>
+  <si>
+    <t>Knight</t>
+  </si>
+  <si>
+    <t>Conquistador</t>
+  </si>
+  <si>
+    <t>King Sancho</t>
+  </si>
+  <si>
+    <t>Bavieca</t>
+  </si>
+  <si>
+    <t>Disappears after El Cid becomes El Cid Campeador</t>
+  </si>
+  <si>
+    <t>Mangonel</t>
+  </si>
+  <si>
+    <t>Pikeman</t>
+  </si>
+  <si>
+    <t>Archer</t>
+  </si>
+  <si>
+    <t>Fishing Boat</t>
+  </si>
+  <si>
+    <t>Missionary</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="14"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Moderate:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+Starting Army:
+3 Light Cavalry
+8 Knights
+4 Conquistdores
+4 Long Swordsmen
+10 Pikemen
+10 Archers
+4 Mangonels
+1 Monk
+Later:
+5 Knights
+12 Long Swordsmen
+2 Missionaries
+Endless Scorpions
+1 Battering Ram
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="14"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Standard:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+Starting Army:
+Identical to Moderate
+Later:
+1 Missionary
+1 Battering Ram
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="14"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Hard:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+Starting Army:
+Identical to Moderate
+Later:
+5 Knights
+12 Long Swordsmen
+4 Missionaries
+Endless Scorpions
+3 Battering Rams</t>
+    </r>
+  </si>
+  <si>
+    <t>King Alfonso</t>
+  </si>
+  <si>
+    <t>Killing him is a Defeat Condition
+Converts to Player</t>
+  </si>
+  <si>
+    <t>Palisade Gate</t>
+  </si>
+  <si>
+    <t>Palisade Wall</t>
+  </si>
+  <si>
+    <t>Pavilion (Large)</t>
+  </si>
+  <si>
+    <t>Cavalier</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="14"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">Moderate:
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">Starting Army:
+ 6 Chavalier
+1 Monk
+Later:
+7 Knights
+10 Long Swordsmen
+2 Monks
+5 Battering Rams
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="14"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Standard:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+Starting Army:
+Identical to Moderate
+Later:
+5 Knights
+5 Battering Rams
+1 Monk
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="14"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Hard:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+Identical to Moderate</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color rgb="FFFFC000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">Long Swordsman </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>(Not on Standard)</t>
+    </r>
+  </si>
+  <si>
+    <t>Camel Rider</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Elite Skirmisher </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>(Not on Standard; 50%)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Mangonel
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>(Not on Standard)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Pikeman
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>(50%)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Crossbowman
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>(50%)</t>
+    </r>
+  </si>
+  <si>
+    <t>Army is either Camel + Skirmisher or Crossbow + Pikeman</t>
+  </si>
+  <si>
+    <t>Some Camels are always there, since they are Starting Units as well</t>
+  </si>
+  <si>
+    <t>Yes, this is unnecessarily complicated.</t>
+  </si>
+  <si>
+    <t>Skirmishers are removed from the Camel-Army on Standard</t>
+  </si>
+  <si>
+    <t>Camel Archer</t>
+  </si>
+  <si>
+    <t>Imam</t>
+  </si>
+  <si>
+    <t>Pavilion</t>
+  </si>
+  <si>
+    <t>Spearman</t>
+  </si>
+  <si>
+    <t>Cavalry Archer</t>
+  </si>
+  <si>
+    <t>Converts to Player</t>
+  </si>
+  <si>
+    <t>Man-at-Arms</t>
+  </si>
+  <si>
+    <t>Throwing Axeman</t>
+  </si>
+  <si>
+    <t>Bombard Tower</t>
+  </si>
+  <si>
+    <t>Mameluke</t>
+  </si>
+  <si>
+    <t>Onager</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="14"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Moderate:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+Starting Army:
+19 Camel Riders
+5 Mamelukes
+8 Camel Archers
+5 Onagers
+Later:
+5 Hussars
+6 Heavy Camel Riders
+10 Heavy Cavalry Archers
+10 Camel Archers
+2 Trebuchets
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="14"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Standard:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+Starting Army:
+10 Camel Riders
+4 Mamelukes
+6 Camel Archers
+Later:
+6 Heavy Camel Riders
+2 Trebuchets
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="14"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Hard:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+Identical to Moderate</t>
+    </r>
+  </si>
+  <si>
+    <t>Hussar</t>
+  </si>
+  <si>
+    <t>Heavy Camel Rider</t>
+  </si>
+  <si>
+    <t>Heavy Cavalry Archer</t>
+  </si>
+  <si>
+    <t>Fishing Ship</t>
+  </si>
+  <si>
+    <t>Transport Ship</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color rgb="FFFFFF00"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>Monk</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">
+(Only on Hard)</t>
+    </r>
+  </si>
+  <si>
+    <t>Carrack</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color rgb="FFFFFF00"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>Galleon</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">
+(Not on Standard)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="14"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Moderate:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+10 Pikemen
+10 Elite Skirmishers
+6 Heavy Camel Riders
+3 Scorpions
+2 Trebuchets
+4 Galleons
+3 Carracks
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="14"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Standard:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+5 Pikemen
+6 Heavy Camel Riders
+2 Trebuchets
+3 Carracks
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="14"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Hard:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+10 Pikemen
+10 Elite Skirmishers
+6 Heavy Camel Riders
+3 Scorpions
+2 Trebuchets
+2 Monks
+4 Galleons
+3 Carracks</t>
+    </r>
+  </si>
+  <si>
+    <t>Dies Early</t>
+  </si>
+  <si>
+    <t>House University</t>
+  </si>
+  <si>
+    <t>Fish Trap</t>
+  </si>
+  <si>
+    <t>Mosque</t>
+  </si>
+  <si>
+    <t>Converting this is a Location</t>
+  </si>
+  <si>
+    <t>Paladin</t>
+  </si>
+  <si>
+    <t>Bombard Cannon</t>
+  </si>
+  <si>
+    <t>Fire Ship</t>
+  </si>
+  <si>
+    <t>Destruction of the Wonder is a Defeat Condition</t>
+  </si>
+  <si>
+    <t>Elite Genitour</t>
+  </si>
+  <si>
+    <t>Elite Cannon Galleon</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color rgb="FFFFFF00"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>Monk</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">
+(Not on Standard)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="14"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Moderate:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+Starting Army:
+3 Galleons
+Later:
+4 Carracks
+8 Galleons
+2 Elite Cannon Galleons
+10 Heavy Cavalry Archers
+2 Elite Genitour
+6 Heavy Camel Riders
+5 Hussars
+4 Capped Rams
+1 Monk
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="14"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Standard:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+Starting Army:
+Identical to Moderate
+Later:
+4 Carracks
+2 Galleons
+10 Heavy Cavalry Archers
+2 Elite Genitour
+6 Heavy Camel Riders
+5 Hussars
+4 Capped Rams
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="14"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Hard:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+Starting Army:
+Identical to Moderate
+Later:
+4 Carracks
+8 Galleons
+3 Elite Cannon Galleons
+10 Heavy Cavalry Archers
+2 Elite Genitour
+6 Heavy Camel Riders
+5 Hussars
+4 Capped Rams
+3 Monks</t>
+    </r>
+  </si>
+  <si>
+    <t>Carracks</t>
+  </si>
+  <si>
+    <t>Yurt</t>
+  </si>
+  <si>
+    <t>Tent</t>
+  </si>
+  <si>
+    <t>Tent (Large)</t>
+  </si>
+  <si>
+    <t>The Tower of Flies</t>
+  </si>
+  <si>
+    <t>The Accursed Tower</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="14"/>
+        <color rgb="FF00B050"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>Fast Fire Ship</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color rgb="FF00B050"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>(Not on Standard)</t>
+    </r>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="25" x14ac:knownFonts="1">
+  <fonts count="30" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -3568,16 +4045,57 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="14"/>
+      <color rgb="FFFFFF00"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="14"/>
+      <color rgb="FF00B050"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="14"/>
+      <color rgb="FF0070C0"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="14"/>
+      <color rgb="FF7030A0"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="14"/>
+      <color rgb="FF06EEFA"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="7">
+  <borders count="11">
     <border>
       <left/>
       <right/>
@@ -3665,11 +4183,59 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -3705,6 +4271,114 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -4124,7 +4798,7 @@
       <c r="K4" s="8"/>
       <c r="L4" s="8"/>
       <c r="M4" s="8" t="s">
-        <v>65</v>
+        <v>131</v>
       </c>
       <c r="N4" s="8"/>
       <c r="O4" s="8"/>
@@ -4154,15 +4828,15 @@
         <v>19</v>
       </c>
       <c r="I5" s="11" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="J5" s="8"/>
       <c r="K5" s="8"/>
       <c r="L5" s="8" t="s">
-        <v>66</v>
+        <v>138</v>
       </c>
       <c r="M5" s="8" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="N5" s="8"/>
       <c r="O5" s="8"/>
@@ -4201,7 +4875,7 @@
       </c>
       <c r="K6" s="8"/>
       <c r="L6" s="8" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="M6" s="8"/>
       <c r="N6" s="8"/>
@@ -4231,22 +4905,22 @@
         <v>54</v>
       </c>
       <c r="H7" s="10" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="I7" s="11" t="s">
-        <v>75</v>
+        <v>71</v>
       </c>
       <c r="J7" s="8" t="s">
         <v>53</v>
       </c>
       <c r="K7" s="8" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="L7" s="8" t="s">
-        <v>70</v>
+        <v>160</v>
       </c>
       <c r="M7" s="8" t="s">
-        <v>72</v>
+        <v>169</v>
       </c>
       <c r="N7" s="8"/>
       <c r="O7" s="8"/>
@@ -4281,7 +4955,7 @@
         <v>56</v>
       </c>
       <c r="J8" s="8" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="K8" s="8"/>
       <c r="L8" s="8"/>
@@ -4314,17 +4988,17 @@
         <v>61</v>
       </c>
       <c r="I9" s="11" t="s">
-        <v>76</v>
+        <v>72</v>
       </c>
       <c r="J9" s="8"/>
       <c r="K9" s="8" t="s">
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="L9" s="8" t="s">
-        <v>78</v>
+        <v>182</v>
       </c>
       <c r="M9" s="8" t="s">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="N9" s="8"/>
       <c r="O9" s="8"/>
@@ -4337,4 +5011,2573 @@
   <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" verticalDpi="0" r:id="rId1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C7806EE9-C3B6-4767-BE4E-BC3AB2AED020}">
+  <dimension ref="G1:L42"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="7" max="8" width="22.5703125" customWidth="1"/>
+    <col min="11" max="12" width="22.5703125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="7:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="2" spans="7:12" ht="47.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G2" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="H2" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="K2" s="2" t="s">
+        <v>119</v>
+      </c>
+      <c r="L2" s="2" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="3" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G3" s="37" t="s">
+        <v>118</v>
+      </c>
+      <c r="H3" s="9" t="s">
+        <v>75</v>
+      </c>
+      <c r="K3" s="29" t="s">
+        <v>92</v>
+      </c>
+      <c r="L3" s="9" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="4" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G4" s="22" t="s">
+        <v>114</v>
+      </c>
+      <c r="H4" s="9" t="s">
+        <v>75</v>
+      </c>
+      <c r="K4" s="23" t="s">
+        <v>90</v>
+      </c>
+      <c r="L4" s="9" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="5" spans="7:12" ht="37.5" x14ac:dyDescent="0.25">
+      <c r="G5" s="26" t="s">
+        <v>77</v>
+      </c>
+      <c r="H5" s="9" t="s">
+        <v>75</v>
+      </c>
+      <c r="K5" s="24" t="s">
+        <v>134</v>
+      </c>
+      <c r="L5" s="9" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="6" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G6" s="14" t="s">
+        <v>123</v>
+      </c>
+      <c r="H6" s="9" t="s">
+        <v>75</v>
+      </c>
+      <c r="K6" s="23" t="s">
+        <v>117</v>
+      </c>
+      <c r="L6" s="9" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="7" spans="7:12" ht="56.25" x14ac:dyDescent="0.25">
+      <c r="G7" s="26" t="s">
+        <v>124</v>
+      </c>
+      <c r="H7" s="9" t="s">
+        <v>125</v>
+      </c>
+      <c r="K7" s="23" t="s">
+        <v>98</v>
+      </c>
+      <c r="L7" s="9" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="8" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G8" s="23" t="s">
+        <v>111</v>
+      </c>
+      <c r="H8" s="9" t="s">
+        <v>75</v>
+      </c>
+      <c r="K8" s="23" t="s">
+        <v>86</v>
+      </c>
+      <c r="L8" s="9" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="9" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G9" s="23" t="s">
+        <v>78</v>
+      </c>
+      <c r="H9" s="9" t="s">
+        <v>75</v>
+      </c>
+      <c r="K9" s="23" t="s">
+        <v>94</v>
+      </c>
+      <c r="L9" s="9" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="10" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G10" s="23" t="s">
+        <v>121</v>
+      </c>
+      <c r="H10" s="9" t="s">
+        <v>75</v>
+      </c>
+      <c r="K10" s="23" t="s">
+        <v>102</v>
+      </c>
+      <c r="L10" s="9" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="11" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G11" s="23" t="s">
+        <v>93</v>
+      </c>
+      <c r="H11" s="9" t="s">
+        <v>75</v>
+      </c>
+      <c r="K11" s="23" t="s">
+        <v>96</v>
+      </c>
+      <c r="L11" s="9" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="12" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G12" s="24" t="s">
+        <v>122</v>
+      </c>
+      <c r="H12" s="9" t="s">
+        <v>75</v>
+      </c>
+      <c r="K12" s="23" t="s">
+        <v>108</v>
+      </c>
+      <c r="L12" s="9" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="13" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G13" s="23" t="s">
+        <v>126</v>
+      </c>
+      <c r="H13" s="9" t="s">
+        <v>75</v>
+      </c>
+      <c r="K13" s="23" t="s">
+        <v>112</v>
+      </c>
+      <c r="L13" s="9" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="14" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G14" s="23" t="s">
+        <v>104</v>
+      </c>
+      <c r="H14" s="9" t="s">
+        <v>75</v>
+      </c>
+      <c r="K14" s="23" t="s">
+        <v>100</v>
+      </c>
+      <c r="L14" s="9" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="15" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G15" s="23" t="s">
+        <v>127</v>
+      </c>
+      <c r="H15" s="9" t="s">
+        <v>75</v>
+      </c>
+      <c r="K15" s="23" t="s">
+        <v>106</v>
+      </c>
+      <c r="L15" s="9" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="16" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G16" s="23" t="s">
+        <v>128</v>
+      </c>
+      <c r="H16" s="9" t="s">
+        <v>75</v>
+      </c>
+      <c r="K16" s="23" t="s">
+        <v>115</v>
+      </c>
+      <c r="L16" s="9" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="17" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G17" s="23" t="s">
+        <v>129</v>
+      </c>
+      <c r="H17" s="9" t="s">
+        <v>75</v>
+      </c>
+      <c r="K17" s="23" t="s">
+        <v>113</v>
+      </c>
+      <c r="L17" s="9" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="18" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G18" s="24" t="s">
+        <v>130</v>
+      </c>
+      <c r="H18" s="9" t="s">
+        <v>75</v>
+      </c>
+      <c r="K18" s="23" t="s">
+        <v>105</v>
+      </c>
+      <c r="L18" s="9" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="19" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G19" s="23" t="s">
+        <v>91</v>
+      </c>
+      <c r="H19" s="9" t="s">
+        <v>75</v>
+      </c>
+      <c r="K19" s="23" t="s">
+        <v>103</v>
+      </c>
+      <c r="L19" s="9" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="20" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G20" s="27" t="s">
+        <v>101</v>
+      </c>
+      <c r="H20" s="17" t="s">
+        <v>75</v>
+      </c>
+      <c r="K20" s="23" t="s">
+        <v>95</v>
+      </c>
+      <c r="L20" s="9" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="21" spans="7:12" ht="75" x14ac:dyDescent="0.25">
+      <c r="G21" s="24" t="s">
+        <v>132</v>
+      </c>
+      <c r="H21" s="9" t="s">
+        <v>133</v>
+      </c>
+      <c r="K21" s="23" t="s">
+        <v>85</v>
+      </c>
+      <c r="L21" s="9" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="22" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G22" s="28"/>
+      <c r="H22" s="28"/>
+      <c r="K22" s="26" t="s">
+        <v>135</v>
+      </c>
+      <c r="L22" s="9" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="23" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G23" s="28"/>
+      <c r="H23" s="28"/>
+      <c r="K23" s="26" t="s">
+        <v>110</v>
+      </c>
+      <c r="L23" s="9" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="24" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G24" s="28"/>
+      <c r="H24" s="28"/>
+      <c r="K24" s="18" t="s">
+        <v>136</v>
+      </c>
+      <c r="L24" s="17" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="25" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G25" s="28"/>
+      <c r="H25" s="28"/>
+      <c r="K25" s="16"/>
+      <c r="L25" s="16"/>
+    </row>
+    <row r="26" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G26" s="28"/>
+      <c r="H26" s="28"/>
+      <c r="K26" s="28"/>
+      <c r="L26" s="28"/>
+    </row>
+    <row r="27" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G27" s="28"/>
+      <c r="H27" s="28"/>
+      <c r="K27" s="28"/>
+      <c r="L27" s="28"/>
+    </row>
+    <row r="28" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G28" s="28"/>
+      <c r="H28" s="28"/>
+      <c r="K28" s="28"/>
+      <c r="L28" s="28"/>
+    </row>
+    <row r="29" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G29" s="28"/>
+      <c r="H29" s="28"/>
+      <c r="K29" s="28"/>
+      <c r="L29" s="28"/>
+    </row>
+    <row r="30" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G30" s="28"/>
+      <c r="H30" s="28"/>
+      <c r="K30" s="28"/>
+      <c r="L30" s="28"/>
+    </row>
+    <row r="31" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G31" s="28"/>
+      <c r="H31" s="28"/>
+      <c r="K31" s="28"/>
+      <c r="L31" s="28"/>
+    </row>
+    <row r="32" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G32" s="28"/>
+      <c r="H32" s="28"/>
+      <c r="K32" s="28"/>
+      <c r="L32" s="28"/>
+    </row>
+    <row r="33" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G33" s="28"/>
+      <c r="H33" s="28"/>
+      <c r="K33" s="28"/>
+      <c r="L33" s="28"/>
+    </row>
+    <row r="34" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G34" s="28"/>
+      <c r="H34" s="28"/>
+      <c r="K34" s="28"/>
+      <c r="L34" s="28"/>
+    </row>
+    <row r="35" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G35" s="28"/>
+      <c r="H35" s="28"/>
+      <c r="K35" s="28"/>
+      <c r="L35" s="28"/>
+    </row>
+    <row r="36" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G36" s="28"/>
+      <c r="H36" s="28"/>
+      <c r="K36" s="28"/>
+      <c r="L36" s="28"/>
+    </row>
+    <row r="37" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G37" s="28"/>
+      <c r="H37" s="28"/>
+      <c r="K37" s="28"/>
+      <c r="L37" s="28"/>
+    </row>
+    <row r="38" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="K38" s="13"/>
+      <c r="L38" s="13"/>
+    </row>
+    <row r="39" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="K39" s="13"/>
+      <c r="L39" s="13"/>
+    </row>
+    <row r="40" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G40" s="13"/>
+      <c r="H40" s="13"/>
+      <c r="K40" s="13"/>
+      <c r="L40" s="13"/>
+    </row>
+    <row r="41" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G41" s="13"/>
+      <c r="H41" s="13"/>
+      <c r="K41" s="13"/>
+      <c r="L41" s="13"/>
+    </row>
+    <row r="42" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G42" s="13"/>
+      <c r="H42" s="13"/>
+      <c r="K42" s="13"/>
+      <c r="L42" s="13"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CDE5F8DB-FD15-4784-84F9-B75AFD37E946}">
+  <dimension ref="A1:L42"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="11.42578125" hidden="1" customWidth="1"/>
+    <col min="2" max="2" width="0.140625" customWidth="1"/>
+    <col min="3" max="3" width="69.85546875" customWidth="1"/>
+    <col min="4" max="4" width="0.140625" hidden="1" customWidth="1"/>
+    <col min="5" max="5" width="11.42578125" hidden="1" customWidth="1"/>
+    <col min="6" max="6" width="12.140625" hidden="1" customWidth="1"/>
+    <col min="7" max="8" width="22.5703125" customWidth="1"/>
+    <col min="11" max="12" width="22.5703125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="3:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="2" spans="3:12" ht="47.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G2" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="H2" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="K2" s="2" t="s">
+        <v>119</v>
+      </c>
+      <c r="L2" s="2" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="3" spans="3:12" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G3" s="37" t="s">
+        <v>116</v>
+      </c>
+      <c r="H3" s="9" t="s">
+        <v>75</v>
+      </c>
+      <c r="K3" s="30" t="s">
+        <v>90</v>
+      </c>
+      <c r="L3" s="9" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="4" spans="3:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G4" s="30" t="s">
+        <v>111</v>
+      </c>
+      <c r="H4" s="9" t="s">
+        <v>75</v>
+      </c>
+      <c r="K4" s="31" t="s">
+        <v>92</v>
+      </c>
+      <c r="L4" s="9" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="5" spans="3:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G5" s="31" t="s">
+        <v>104</v>
+      </c>
+      <c r="H5" s="9" t="s">
+        <v>75</v>
+      </c>
+      <c r="K5" s="31" t="s">
+        <v>115</v>
+      </c>
+      <c r="L5" s="9" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="6" spans="3:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G6" s="31" t="s">
+        <v>137</v>
+      </c>
+      <c r="H6" s="9" t="s">
+        <v>75</v>
+      </c>
+      <c r="K6" s="31" t="s">
+        <v>110</v>
+      </c>
+      <c r="L6" s="9" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="7" spans="3:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G7" s="31" t="s">
+        <v>101</v>
+      </c>
+      <c r="H7" s="9" t="s">
+        <v>75</v>
+      </c>
+      <c r="K7" s="31" t="s">
+        <v>106</v>
+      </c>
+      <c r="L7" s="9" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="8" spans="3:12" ht="37.5" x14ac:dyDescent="0.25">
+      <c r="G8" s="10" t="s">
+        <v>139</v>
+      </c>
+      <c r="H8" s="9" t="s">
+        <v>75</v>
+      </c>
+      <c r="K8" s="31" t="s">
+        <v>112</v>
+      </c>
+      <c r="L8" s="9" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="9" spans="3:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G9" s="31" t="s">
+        <v>121</v>
+      </c>
+      <c r="H9" s="9" t="s">
+        <v>75</v>
+      </c>
+      <c r="K9" s="31" t="s">
+        <v>100</v>
+      </c>
+      <c r="L9" s="9" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="10" spans="3:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G10" s="20" t="s">
+        <v>140</v>
+      </c>
+      <c r="H10" s="9" t="s">
+        <v>75</v>
+      </c>
+      <c r="K10" s="31" t="s">
+        <v>86</v>
+      </c>
+      <c r="L10" s="9" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="11" spans="3:12" ht="56.25" x14ac:dyDescent="0.25">
+      <c r="C11" s="10" t="s">
+        <v>145</v>
+      </c>
+      <c r="G11" s="20" t="s">
+        <v>141</v>
+      </c>
+      <c r="H11" s="9" t="s">
+        <v>75</v>
+      </c>
+      <c r="K11" s="31" t="s">
+        <v>151</v>
+      </c>
+      <c r="L11" s="9" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="12" spans="3:12" ht="37.5" x14ac:dyDescent="0.25">
+      <c r="C12" s="10" t="s">
+        <v>146</v>
+      </c>
+      <c r="G12" s="20" t="s">
+        <v>143</v>
+      </c>
+      <c r="H12" s="9" t="s">
+        <v>75</v>
+      </c>
+      <c r="K12" s="31" t="s">
+        <v>136</v>
+      </c>
+      <c r="L12" s="9" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="13" spans="3:12" ht="37.5" x14ac:dyDescent="0.25">
+      <c r="C13" s="10" t="s">
+        <v>148</v>
+      </c>
+      <c r="G13" s="20" t="s">
+        <v>144</v>
+      </c>
+      <c r="H13" s="9" t="s">
+        <v>75</v>
+      </c>
+      <c r="K13" s="31" t="s">
+        <v>117</v>
+      </c>
+      <c r="L13" s="9" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="14" spans="3:12" ht="37.5" x14ac:dyDescent="0.25">
+      <c r="C14" s="10" t="s">
+        <v>147</v>
+      </c>
+      <c r="G14" s="20" t="s">
+        <v>142</v>
+      </c>
+      <c r="H14" s="9" t="s">
+        <v>75</v>
+      </c>
+      <c r="K14" s="31" t="s">
+        <v>108</v>
+      </c>
+      <c r="L14" s="9" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="15" spans="3:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G15" s="44" t="s">
+        <v>84</v>
+      </c>
+      <c r="H15" s="9" t="s">
+        <v>81</v>
+      </c>
+      <c r="K15" s="31" t="s">
+        <v>96</v>
+      </c>
+      <c r="L15" s="9" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="16" spans="3:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G16" s="32" t="s">
+        <v>149</v>
+      </c>
+      <c r="H16" s="9" t="s">
+        <v>75</v>
+      </c>
+      <c r="K16" s="31" t="s">
+        <v>113</v>
+      </c>
+      <c r="L16" s="9" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="17" spans="7:12" ht="37.5" x14ac:dyDescent="0.25">
+      <c r="G17" s="46" t="s">
+        <v>150</v>
+      </c>
+      <c r="H17" s="9" t="s">
+        <v>80</v>
+      </c>
+      <c r="K17" s="31" t="s">
+        <v>98</v>
+      </c>
+      <c r="L17" s="9" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="18" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G18" s="28"/>
+      <c r="H18" s="28"/>
+      <c r="K18" s="31" t="s">
+        <v>95</v>
+      </c>
+      <c r="L18" s="9" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="19" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G19" s="28"/>
+      <c r="H19" s="28"/>
+      <c r="K19" s="31" t="s">
+        <v>102</v>
+      </c>
+      <c r="L19" s="9" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="20" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G20" s="28"/>
+      <c r="H20" s="28"/>
+      <c r="K20" s="31" t="s">
+        <v>103</v>
+      </c>
+      <c r="L20" s="9" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="21" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G21" s="28"/>
+      <c r="H21" s="28"/>
+      <c r="K21" s="31" t="s">
+        <v>94</v>
+      </c>
+      <c r="L21" s="9" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="22" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G22" s="28"/>
+      <c r="H22" s="28"/>
+      <c r="K22" s="31" t="s">
+        <v>85</v>
+      </c>
+      <c r="L22" s="9" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="23" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G23" s="28"/>
+      <c r="H23" s="28"/>
+      <c r="K23" s="31" t="s">
+        <v>135</v>
+      </c>
+      <c r="L23" s="9" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="24" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G24" s="28"/>
+      <c r="H24" s="28"/>
+      <c r="K24" s="20" t="s">
+        <v>105</v>
+      </c>
+      <c r="L24" s="9" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="25" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G25" s="28"/>
+      <c r="H25" s="28"/>
+      <c r="K25" s="35" t="s">
+        <v>87</v>
+      </c>
+      <c r="L25" s="17" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="26" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G26" s="28"/>
+      <c r="H26" s="28"/>
+      <c r="K26" s="16"/>
+      <c r="L26" s="16"/>
+    </row>
+    <row r="27" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G27" s="28"/>
+      <c r="H27" s="28"/>
+      <c r="K27" s="28"/>
+      <c r="L27" s="28"/>
+    </row>
+    <row r="28" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G28" s="28"/>
+      <c r="H28" s="28"/>
+      <c r="K28" s="28"/>
+      <c r="L28" s="28"/>
+    </row>
+    <row r="29" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G29" s="28"/>
+      <c r="H29" s="28"/>
+      <c r="K29" s="28"/>
+      <c r="L29" s="28"/>
+    </row>
+    <row r="30" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G30" s="28"/>
+      <c r="H30" s="28"/>
+      <c r="K30" s="28"/>
+      <c r="L30" s="28"/>
+    </row>
+    <row r="31" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G31" s="28"/>
+      <c r="H31" s="28"/>
+      <c r="K31" s="28"/>
+      <c r="L31" s="28"/>
+    </row>
+    <row r="32" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G32" s="28"/>
+      <c r="H32" s="28"/>
+      <c r="K32" s="28"/>
+      <c r="L32" s="28"/>
+    </row>
+    <row r="33" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G33" s="28"/>
+      <c r="H33" s="28"/>
+      <c r="K33" s="28"/>
+      <c r="L33" s="28"/>
+    </row>
+    <row r="34" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G34" s="28"/>
+      <c r="H34" s="28"/>
+      <c r="K34" s="28"/>
+      <c r="L34" s="28"/>
+    </row>
+    <row r="35" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G35" s="28"/>
+      <c r="H35" s="28"/>
+      <c r="K35" s="28"/>
+      <c r="L35" s="28"/>
+    </row>
+    <row r="36" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G36" s="28"/>
+      <c r="H36" s="28"/>
+      <c r="K36" s="28"/>
+      <c r="L36" s="28"/>
+    </row>
+    <row r="37" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G37" s="28"/>
+      <c r="H37" s="28"/>
+      <c r="K37" s="28"/>
+      <c r="L37" s="28"/>
+    </row>
+    <row r="38" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="K38" s="13"/>
+      <c r="L38" s="13"/>
+    </row>
+    <row r="39" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="K39" s="13"/>
+      <c r="L39" s="13"/>
+    </row>
+    <row r="40" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G40" s="13"/>
+      <c r="H40" s="13"/>
+      <c r="K40" s="13"/>
+      <c r="L40" s="13"/>
+    </row>
+    <row r="41" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G41" s="13"/>
+      <c r="H41" s="13"/>
+      <c r="K41" s="13"/>
+      <c r="L41" s="13"/>
+    </row>
+    <row r="42" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G42" s="13"/>
+      <c r="H42" s="13"/>
+      <c r="K42" s="13"/>
+      <c r="L42" s="13"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{35CC0715-C907-4E5C-AD21-1C53B8AEFAF6}">
+  <dimension ref="G1:L42"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="7" max="8" width="22.5703125" customWidth="1"/>
+    <col min="11" max="12" width="22.5703125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="7:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="2" spans="7:12" ht="47.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G2" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="H2" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="K2" s="2" t="s">
+        <v>119</v>
+      </c>
+      <c r="L2" s="2" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="3" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G3" s="7" t="s">
+        <v>116</v>
+      </c>
+      <c r="H3" s="9" t="s">
+        <v>75</v>
+      </c>
+      <c r="K3" s="29" t="s">
+        <v>92</v>
+      </c>
+      <c r="L3" s="9" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="4" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G4" s="10" t="s">
+        <v>114</v>
+      </c>
+      <c r="H4" s="9" t="s">
+        <v>75</v>
+      </c>
+      <c r="K4" s="23" t="s">
+        <v>90</v>
+      </c>
+      <c r="L4" s="9" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="5" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G5" s="45" t="s">
+        <v>152</v>
+      </c>
+      <c r="H5" s="9" t="s">
+        <v>75</v>
+      </c>
+      <c r="K5" s="23" t="s">
+        <v>86</v>
+      </c>
+      <c r="L5" s="9" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="6" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G6" s="23" t="s">
+        <v>127</v>
+      </c>
+      <c r="H6" s="9" t="s">
+        <v>75</v>
+      </c>
+      <c r="K6" s="23" t="s">
+        <v>157</v>
+      </c>
+      <c r="L6" s="9" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="7" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G7" s="23" t="s">
+        <v>128</v>
+      </c>
+      <c r="H7" s="9" t="s">
+        <v>75</v>
+      </c>
+      <c r="K7" s="23" t="s">
+        <v>108</v>
+      </c>
+      <c r="L7" s="9" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="8" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G8" s="23" t="s">
+        <v>91</v>
+      </c>
+      <c r="H8" s="9" t="s">
+        <v>75</v>
+      </c>
+      <c r="K8" s="23" t="s">
+        <v>113</v>
+      </c>
+      <c r="L8" s="9" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="9" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G9" s="23" t="s">
+        <v>78</v>
+      </c>
+      <c r="H9" s="9" t="s">
+        <v>75</v>
+      </c>
+      <c r="K9" s="23" t="s">
+        <v>94</v>
+      </c>
+      <c r="L9" s="9" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="10" spans="7:12" ht="56.25" x14ac:dyDescent="0.25">
+      <c r="G10" s="23" t="s">
+        <v>124</v>
+      </c>
+      <c r="H10" s="9" t="s">
+        <v>125</v>
+      </c>
+      <c r="K10" s="23" t="s">
+        <v>117</v>
+      </c>
+      <c r="L10" s="9" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="11" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G11" s="32" t="s">
+        <v>140</v>
+      </c>
+      <c r="H11" s="9" t="s">
+        <v>154</v>
+      </c>
+      <c r="K11" s="23" t="s">
+        <v>96</v>
+      </c>
+      <c r="L11" s="9" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="12" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G12" s="32" t="s">
+        <v>153</v>
+      </c>
+      <c r="H12" s="9" t="s">
+        <v>154</v>
+      </c>
+      <c r="K12" s="23" t="s">
+        <v>106</v>
+      </c>
+      <c r="L12" s="9" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="13" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G13" s="46" t="s">
+        <v>155</v>
+      </c>
+      <c r="H13" s="9" t="s">
+        <v>75</v>
+      </c>
+      <c r="K13" s="23" t="s">
+        <v>103</v>
+      </c>
+      <c r="L13" s="9" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="14" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G14" s="33" t="s">
+        <v>126</v>
+      </c>
+      <c r="H14" s="9" t="s">
+        <v>75</v>
+      </c>
+      <c r="K14" s="23" t="s">
+        <v>85</v>
+      </c>
+      <c r="L14" s="9" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="15" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G15" s="33" t="s">
+        <v>101</v>
+      </c>
+      <c r="H15" s="9" t="s">
+        <v>75</v>
+      </c>
+      <c r="K15" s="23" t="s">
+        <v>87</v>
+      </c>
+      <c r="L15" s="9" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="16" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G16" s="33" t="s">
+        <v>104</v>
+      </c>
+      <c r="H16" s="9" t="s">
+        <v>75</v>
+      </c>
+      <c r="K16" s="32" t="s">
+        <v>105</v>
+      </c>
+      <c r="L16" s="9" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="17" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G17" s="33" t="s">
+        <v>121</v>
+      </c>
+      <c r="H17" s="9" t="s">
+        <v>75</v>
+      </c>
+      <c r="K17" s="32" t="s">
+        <v>98</v>
+      </c>
+      <c r="L17" s="9" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="18" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G18" s="33" t="s">
+        <v>93</v>
+      </c>
+      <c r="H18" s="9" t="s">
+        <v>75</v>
+      </c>
+      <c r="K18" s="33" t="s">
+        <v>102</v>
+      </c>
+      <c r="L18" s="9" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="19" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G19" s="33" t="s">
+        <v>109</v>
+      </c>
+      <c r="H19" s="9" t="s">
+        <v>75</v>
+      </c>
+      <c r="K19" s="33" t="s">
+        <v>100</v>
+      </c>
+      <c r="L19" s="9" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="20" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G20" s="46" t="s">
+        <v>156</v>
+      </c>
+      <c r="H20" s="9" t="s">
+        <v>75</v>
+      </c>
+      <c r="K20" s="33" t="s">
+        <v>112</v>
+      </c>
+      <c r="L20" s="9" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="21" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G21" s="28"/>
+      <c r="H21" s="28"/>
+      <c r="K21" s="34" t="s">
+        <v>95</v>
+      </c>
+      <c r="L21" s="17" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="22" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G22" s="28"/>
+      <c r="H22" s="28"/>
+      <c r="K22" s="33" t="s">
+        <v>151</v>
+      </c>
+      <c r="L22" s="9" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="23" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G23" s="28"/>
+      <c r="H23" s="28"/>
+      <c r="K23" s="33" t="s">
+        <v>136</v>
+      </c>
+      <c r="L23" s="9" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="24" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G24" s="28"/>
+      <c r="H24" s="28"/>
+      <c r="K24" s="28"/>
+      <c r="L24" s="28"/>
+    </row>
+    <row r="25" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G25" s="28"/>
+      <c r="H25" s="28"/>
+      <c r="K25" s="28"/>
+      <c r="L25" s="28"/>
+    </row>
+    <row r="26" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G26" s="28"/>
+      <c r="H26" s="28"/>
+      <c r="K26" s="28"/>
+      <c r="L26" s="28"/>
+    </row>
+    <row r="27" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G27" s="28"/>
+      <c r="H27" s="28"/>
+      <c r="K27" s="28"/>
+      <c r="L27" s="28"/>
+    </row>
+    <row r="28" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G28" s="28"/>
+      <c r="H28" s="28"/>
+      <c r="K28" s="28"/>
+      <c r="L28" s="28"/>
+    </row>
+    <row r="29" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G29" s="28"/>
+      <c r="H29" s="28"/>
+      <c r="K29" s="28"/>
+      <c r="L29" s="28"/>
+    </row>
+    <row r="30" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G30" s="28"/>
+      <c r="H30" s="28"/>
+      <c r="K30" s="28"/>
+      <c r="L30" s="28"/>
+    </row>
+    <row r="31" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G31" s="28"/>
+      <c r="H31" s="28"/>
+      <c r="K31" s="28"/>
+      <c r="L31" s="28"/>
+    </row>
+    <row r="32" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G32" s="28"/>
+      <c r="H32" s="28"/>
+      <c r="K32" s="28"/>
+      <c r="L32" s="28"/>
+    </row>
+    <row r="33" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G33" s="28"/>
+      <c r="H33" s="28"/>
+      <c r="K33" s="28"/>
+      <c r="L33" s="28"/>
+    </row>
+    <row r="34" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G34" s="28"/>
+      <c r="H34" s="28"/>
+      <c r="K34" s="28"/>
+      <c r="L34" s="28"/>
+    </row>
+    <row r="35" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G35" s="28"/>
+      <c r="H35" s="28"/>
+      <c r="K35" s="28"/>
+      <c r="L35" s="28"/>
+    </row>
+    <row r="36" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G36" s="28"/>
+      <c r="H36" s="28"/>
+      <c r="K36" s="28"/>
+      <c r="L36" s="28"/>
+    </row>
+    <row r="37" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G37" s="28"/>
+      <c r="H37" s="28"/>
+      <c r="K37" s="28"/>
+      <c r="L37" s="28"/>
+    </row>
+    <row r="38" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="K38" s="13"/>
+      <c r="L38" s="13"/>
+    </row>
+    <row r="39" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="K39" s="13"/>
+      <c r="L39" s="13"/>
+    </row>
+    <row r="40" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G40" s="13"/>
+      <c r="H40" s="13"/>
+      <c r="K40" s="13"/>
+      <c r="L40" s="13"/>
+    </row>
+    <row r="41" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G41" s="13"/>
+      <c r="H41" s="13"/>
+      <c r="K41" s="13"/>
+      <c r="L41" s="13"/>
+    </row>
+    <row r="42" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G42" s="13"/>
+      <c r="H42" s="13"/>
+      <c r="K42" s="13"/>
+      <c r="L42" s="13"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D504A7F2-3BD6-44D6-BE88-D138677C7901}">
+  <dimension ref="G1:L42"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="7" max="8" width="22.5703125" customWidth="1"/>
+    <col min="11" max="12" width="22.5703125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="7:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="2" spans="7:12" ht="47.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G2" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="H2" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="K2" s="2" t="s">
+        <v>119</v>
+      </c>
+      <c r="L2" s="2" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="3" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G3" s="10" t="s">
+        <v>118</v>
+      </c>
+      <c r="H3" s="9" t="s">
+        <v>75</v>
+      </c>
+      <c r="K3" s="41" t="s">
+        <v>92</v>
+      </c>
+      <c r="L3" s="9" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="4" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G4" s="10" t="s">
+        <v>114</v>
+      </c>
+      <c r="H4" s="9" t="s">
+        <v>75</v>
+      </c>
+      <c r="K4" s="26" t="s">
+        <v>90</v>
+      </c>
+      <c r="L4" s="9" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="5" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G5" s="38" t="s">
+        <v>121</v>
+      </c>
+      <c r="H5" s="9" t="s">
+        <v>75</v>
+      </c>
+      <c r="K5" s="26" t="s">
+        <v>135</v>
+      </c>
+      <c r="L5" s="9" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="6" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G6" s="32" t="s">
+        <v>140</v>
+      </c>
+      <c r="H6" s="9" t="s">
+        <v>75</v>
+      </c>
+      <c r="K6" s="26" t="s">
+        <v>112</v>
+      </c>
+      <c r="L6" s="9" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="7" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G7" s="32" t="s">
+        <v>153</v>
+      </c>
+      <c r="H7" s="9" t="s">
+        <v>75</v>
+      </c>
+      <c r="K7" s="26" t="s">
+        <v>100</v>
+      </c>
+      <c r="L7" s="9" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="8" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G8" s="47" t="s">
+        <v>158</v>
+      </c>
+      <c r="H8" s="9" t="s">
+        <v>75</v>
+      </c>
+      <c r="K8" s="26" t="s">
+        <v>106</v>
+      </c>
+      <c r="L8" s="9" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="9" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G9" s="32" t="s">
+        <v>93</v>
+      </c>
+      <c r="H9" s="9" t="s">
+        <v>75</v>
+      </c>
+      <c r="K9" s="26" t="s">
+        <v>115</v>
+      </c>
+      <c r="L9" s="9" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="10" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G10" s="32" t="s">
+        <v>111</v>
+      </c>
+      <c r="H10" s="9" t="s">
+        <v>75</v>
+      </c>
+      <c r="K10" s="26" t="s">
+        <v>110</v>
+      </c>
+      <c r="L10" s="9" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="11" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G11" s="32" t="s">
+        <v>101</v>
+      </c>
+      <c r="H11" s="9" t="s">
+        <v>75</v>
+      </c>
+      <c r="K11" s="26" t="s">
+        <v>86</v>
+      </c>
+      <c r="L11" s="9" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="12" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G12" s="20" t="s">
+        <v>159</v>
+      </c>
+      <c r="H12" s="9" t="s">
+        <v>75</v>
+      </c>
+      <c r="K12" s="26" t="s">
+        <v>171</v>
+      </c>
+      <c r="L12" s="9" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="13" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G13" s="20" t="s">
+        <v>149</v>
+      </c>
+      <c r="H13" s="9" t="s">
+        <v>75</v>
+      </c>
+      <c r="K13" s="26" t="s">
+        <v>95</v>
+      </c>
+      <c r="L13" s="9" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="14" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G14" s="20" t="s">
+        <v>161</v>
+      </c>
+      <c r="H14" s="9" t="s">
+        <v>75</v>
+      </c>
+      <c r="K14" s="26" t="s">
+        <v>103</v>
+      </c>
+      <c r="L14" s="9" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="15" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G15" s="20" t="s">
+        <v>162</v>
+      </c>
+      <c r="H15" s="9" t="s">
+        <v>75</v>
+      </c>
+      <c r="K15" s="26" t="s">
+        <v>85</v>
+      </c>
+      <c r="L15" s="9" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="16" spans="7:12" ht="37.5" x14ac:dyDescent="0.25">
+      <c r="G16" s="20" t="s">
+        <v>163</v>
+      </c>
+      <c r="H16" s="9" t="s">
+        <v>75</v>
+      </c>
+      <c r="K16" s="26" t="s">
+        <v>102</v>
+      </c>
+      <c r="L16" s="9" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="17" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G17" s="20" t="s">
+        <v>88</v>
+      </c>
+      <c r="H17" s="9" t="s">
+        <v>75</v>
+      </c>
+      <c r="K17" s="26" t="s">
+        <v>96</v>
+      </c>
+      <c r="L17" s="9" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="18" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G18" s="26" t="s">
+        <v>164</v>
+      </c>
+      <c r="H18" s="9" t="s">
+        <v>75</v>
+      </c>
+      <c r="K18" s="26" t="s">
+        <v>105</v>
+      </c>
+      <c r="L18" s="9" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="19" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G19" s="26" t="s">
+        <v>165</v>
+      </c>
+      <c r="H19" s="9" t="s">
+        <v>75</v>
+      </c>
+      <c r="K19" s="26" t="s">
+        <v>108</v>
+      </c>
+      <c r="L19" s="9" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="20" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G20" s="26" t="s">
+        <v>127</v>
+      </c>
+      <c r="H20" s="9" t="s">
+        <v>75</v>
+      </c>
+      <c r="K20" s="26" t="s">
+        <v>113</v>
+      </c>
+      <c r="L20" s="9" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="21" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G21" s="26" t="s">
+        <v>79</v>
+      </c>
+      <c r="H21" s="9" t="s">
+        <v>75</v>
+      </c>
+      <c r="K21" s="26" t="s">
+        <v>94</v>
+      </c>
+      <c r="L21" s="9" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="22" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G22" s="26" t="s">
+        <v>91</v>
+      </c>
+      <c r="H22" s="9" t="s">
+        <v>75</v>
+      </c>
+      <c r="K22" s="26" t="s">
+        <v>172</v>
+      </c>
+      <c r="L22" s="9" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="23" spans="7:12" ht="37.5" x14ac:dyDescent="0.25">
+      <c r="G23" s="10" t="s">
+        <v>166</v>
+      </c>
+      <c r="H23" s="9" t="s">
+        <v>75</v>
+      </c>
+      <c r="K23" s="14" t="s">
+        <v>173</v>
+      </c>
+      <c r="L23" s="9" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="24" spans="7:12" ht="37.5" x14ac:dyDescent="0.25">
+      <c r="G24" s="10" t="s">
+        <v>168</v>
+      </c>
+      <c r="H24" s="9" t="s">
+        <v>75</v>
+      </c>
+      <c r="K24" s="32" t="s">
+        <v>151</v>
+      </c>
+      <c r="L24" s="9" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="25" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G25" s="39" t="s">
+        <v>167</v>
+      </c>
+      <c r="H25" s="17" t="s">
+        <v>75</v>
+      </c>
+      <c r="K25" s="32" t="s">
+        <v>136</v>
+      </c>
+      <c r="L25" s="9" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="26" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G26" s="27" t="s">
+        <v>128</v>
+      </c>
+      <c r="H26" s="17" t="s">
+        <v>170</v>
+      </c>
+      <c r="K26" s="27" t="s">
+        <v>87</v>
+      </c>
+      <c r="L26" s="17" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="27" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G27" s="40"/>
+      <c r="H27" s="16"/>
+      <c r="K27" s="16"/>
+      <c r="L27" s="16"/>
+    </row>
+    <row r="28" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G28" s="28"/>
+      <c r="H28" s="28"/>
+      <c r="K28" s="28"/>
+      <c r="L28" s="28"/>
+    </row>
+    <row r="29" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G29" s="28"/>
+      <c r="H29" s="28"/>
+      <c r="K29" s="28"/>
+      <c r="L29" s="28"/>
+    </row>
+    <row r="30" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G30" s="28"/>
+      <c r="H30" s="28"/>
+      <c r="K30" s="28"/>
+      <c r="L30" s="28"/>
+    </row>
+    <row r="31" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G31" s="28"/>
+      <c r="H31" s="28"/>
+      <c r="K31" s="28"/>
+      <c r="L31" s="28"/>
+    </row>
+    <row r="32" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G32" s="28"/>
+      <c r="H32" s="28"/>
+      <c r="K32" s="28"/>
+      <c r="L32" s="28"/>
+    </row>
+    <row r="33" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G33" s="28"/>
+      <c r="H33" s="28"/>
+      <c r="K33" s="28"/>
+      <c r="L33" s="28"/>
+    </row>
+    <row r="34" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G34" s="28"/>
+      <c r="H34" s="28"/>
+      <c r="K34" s="28"/>
+      <c r="L34" s="28"/>
+    </row>
+    <row r="35" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G35" s="28"/>
+      <c r="H35" s="28"/>
+      <c r="K35" s="28"/>
+      <c r="L35" s="28"/>
+    </row>
+    <row r="36" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G36" s="28"/>
+      <c r="H36" s="28"/>
+      <c r="K36" s="28"/>
+      <c r="L36" s="28"/>
+    </row>
+    <row r="37" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G37" s="28"/>
+      <c r="H37" s="28"/>
+      <c r="K37" s="28"/>
+      <c r="L37" s="28"/>
+    </row>
+    <row r="38" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="K38" s="13"/>
+      <c r="L38" s="13"/>
+    </row>
+    <row r="39" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="K39" s="13"/>
+      <c r="L39" s="13"/>
+    </row>
+    <row r="40" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G40" s="13"/>
+      <c r="H40" s="13"/>
+      <c r="K40" s="13"/>
+      <c r="L40" s="13"/>
+    </row>
+    <row r="41" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G41" s="13"/>
+      <c r="H41" s="13"/>
+      <c r="K41" s="13"/>
+      <c r="L41" s="13"/>
+    </row>
+    <row r="42" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G42" s="13"/>
+      <c r="H42" s="13"/>
+      <c r="K42" s="13"/>
+      <c r="L42" s="13"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5FBE6260-452E-4DFF-B03C-024D06C3012A}">
+  <dimension ref="G1:L42"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="7" max="8" width="22.5703125" customWidth="1"/>
+    <col min="11" max="12" width="22.5703125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="7:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="2" spans="7:12" ht="47.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G2" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="H2" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="K2" s="2" t="s">
+        <v>119</v>
+      </c>
+      <c r="L2" s="2" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="3" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G3" s="25" t="s">
+        <v>118</v>
+      </c>
+      <c r="H3" s="9" t="s">
+        <v>75</v>
+      </c>
+      <c r="K3" s="42" t="s">
+        <v>90</v>
+      </c>
+      <c r="L3" s="9" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="4" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G4" s="33" t="s">
+        <v>128</v>
+      </c>
+      <c r="H4" s="9" t="s">
+        <v>75</v>
+      </c>
+      <c r="K4" s="46" t="s">
+        <v>89</v>
+      </c>
+      <c r="L4" s="9" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="5" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G5" s="33" t="s">
+        <v>127</v>
+      </c>
+      <c r="H5" s="9" t="s">
+        <v>75</v>
+      </c>
+      <c r="K5" s="33" t="s">
+        <v>86</v>
+      </c>
+      <c r="L5" s="9" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="6" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G6" s="33" t="s">
+        <v>78</v>
+      </c>
+      <c r="H6" s="9" t="s">
+        <v>75</v>
+      </c>
+      <c r="K6" s="33" t="s">
+        <v>117</v>
+      </c>
+      <c r="L6" s="9" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="7" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G7" s="46" t="s">
+        <v>107</v>
+      </c>
+      <c r="H7" s="9" t="s">
+        <v>75</v>
+      </c>
+      <c r="K7" s="33" t="s">
+        <v>157</v>
+      </c>
+      <c r="L7" s="9" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="8" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G8" s="33" t="s">
+        <v>121</v>
+      </c>
+      <c r="H8" s="9" t="s">
+        <v>75</v>
+      </c>
+      <c r="K8" s="33" t="s">
+        <v>94</v>
+      </c>
+      <c r="L8" s="9" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="9" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G9" s="33" t="s">
+        <v>91</v>
+      </c>
+      <c r="H9" s="9" t="s">
+        <v>75</v>
+      </c>
+      <c r="K9" s="33" t="s">
+        <v>96</v>
+      </c>
+      <c r="L9" s="9" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="10" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G10" s="33" t="s">
+        <v>101</v>
+      </c>
+      <c r="H10" s="9" t="s">
+        <v>75</v>
+      </c>
+      <c r="K10" s="33" t="s">
+        <v>108</v>
+      </c>
+      <c r="L10" s="9" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="11" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G11" s="33" t="s">
+        <v>88</v>
+      </c>
+      <c r="H11" s="9" t="s">
+        <v>75</v>
+      </c>
+      <c r="K11" s="33" t="s">
+        <v>105</v>
+      </c>
+      <c r="L11" s="9" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="12" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G12" s="33" t="s">
+        <v>111</v>
+      </c>
+      <c r="H12" s="9" t="s">
+        <v>75</v>
+      </c>
+      <c r="K12" s="33" t="s">
+        <v>113</v>
+      </c>
+      <c r="L12" s="9" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="13" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G13" s="33" t="s">
+        <v>137</v>
+      </c>
+      <c r="H13" s="9" t="s">
+        <v>75</v>
+      </c>
+      <c r="K13" s="33" t="s">
+        <v>95</v>
+      </c>
+      <c r="L13" s="9" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="14" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G14" s="46" t="s">
+        <v>175</v>
+      </c>
+      <c r="H14" s="9" t="s">
+        <v>75</v>
+      </c>
+      <c r="K14" s="33" t="s">
+        <v>98</v>
+      </c>
+      <c r="L14" s="9" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="15" spans="7:12" ht="37.5" x14ac:dyDescent="0.25">
+      <c r="G15" s="33" t="s">
+        <v>77</v>
+      </c>
+      <c r="H15" s="9" t="s">
+        <v>75</v>
+      </c>
+      <c r="K15" s="33" t="s">
+        <v>110</v>
+      </c>
+      <c r="L15" s="9" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="16" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G16" s="46" t="s">
+        <v>76</v>
+      </c>
+      <c r="H16" s="9" t="s">
+        <v>75</v>
+      </c>
+      <c r="K16" s="33" t="s">
+        <v>103</v>
+      </c>
+      <c r="L16" s="9" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="17" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G17" s="33" t="s">
+        <v>126</v>
+      </c>
+      <c r="H17" s="9" t="s">
+        <v>75</v>
+      </c>
+      <c r="K17" s="33" t="s">
+        <v>102</v>
+      </c>
+      <c r="L17" s="9" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="18" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G18" s="46" t="s">
+        <v>176</v>
+      </c>
+      <c r="H18" s="9" t="s">
+        <v>75</v>
+      </c>
+      <c r="K18" s="33" t="s">
+        <v>112</v>
+      </c>
+      <c r="L18" s="9" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="19" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G19" s="15" t="s">
+        <v>177</v>
+      </c>
+      <c r="H19" s="17" t="s">
+        <v>75</v>
+      </c>
+      <c r="K19" s="20" t="s">
+        <v>92</v>
+      </c>
+      <c r="L19" s="9" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="20" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G20" s="16"/>
+      <c r="H20" s="16"/>
+      <c r="K20" s="20" t="s">
+        <v>135</v>
+      </c>
+      <c r="L20" s="9" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="21" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G21" s="28"/>
+      <c r="H21" s="28"/>
+      <c r="K21" s="20" t="s">
+        <v>87</v>
+      </c>
+      <c r="L21" s="9" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="22" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G22" s="28"/>
+      <c r="H22" s="28"/>
+      <c r="K22" s="31" t="s">
+        <v>151</v>
+      </c>
+      <c r="L22" s="9" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="23" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G23" s="28"/>
+      <c r="H23" s="28"/>
+      <c r="K23" s="31" t="s">
+        <v>106</v>
+      </c>
+      <c r="L23" s="9" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="24" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G24" s="28"/>
+      <c r="H24" s="28"/>
+      <c r="K24" s="31" t="s">
+        <v>85</v>
+      </c>
+      <c r="L24" s="9" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="25" spans="7:12" ht="56.25" x14ac:dyDescent="0.25">
+      <c r="G25" s="28"/>
+      <c r="H25" s="28"/>
+      <c r="K25" s="15" t="s">
+        <v>83</v>
+      </c>
+      <c r="L25" s="17" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="26" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G26" s="28"/>
+      <c r="H26" s="28"/>
+      <c r="K26" s="16"/>
+      <c r="L26" s="16"/>
+    </row>
+    <row r="27" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G27" s="28"/>
+      <c r="H27" s="28"/>
+      <c r="K27" s="28"/>
+      <c r="L27" s="28"/>
+    </row>
+    <row r="28" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G28" s="28"/>
+      <c r="H28" s="28"/>
+      <c r="K28" s="28"/>
+      <c r="L28" s="28"/>
+    </row>
+    <row r="29" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G29" s="28"/>
+      <c r="H29" s="28"/>
+      <c r="K29" s="28"/>
+      <c r="L29" s="28"/>
+    </row>
+    <row r="30" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G30" s="28"/>
+      <c r="H30" s="28"/>
+      <c r="K30" s="28"/>
+      <c r="L30" s="28"/>
+    </row>
+    <row r="31" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G31" s="28"/>
+      <c r="H31" s="28"/>
+      <c r="K31" s="28"/>
+      <c r="L31" s="28"/>
+    </row>
+    <row r="32" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G32" s="28"/>
+      <c r="H32" s="28"/>
+      <c r="K32" s="28"/>
+      <c r="L32" s="28"/>
+    </row>
+    <row r="33" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G33" s="28"/>
+      <c r="H33" s="28"/>
+      <c r="K33" s="28"/>
+      <c r="L33" s="28"/>
+    </row>
+    <row r="34" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G34" s="28"/>
+      <c r="H34" s="28"/>
+      <c r="K34" s="28"/>
+      <c r="L34" s="28"/>
+    </row>
+    <row r="35" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G35" s="28"/>
+      <c r="H35" s="28"/>
+      <c r="K35" s="28"/>
+      <c r="L35" s="28"/>
+    </row>
+    <row r="36" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G36" s="28"/>
+      <c r="H36" s="28"/>
+      <c r="K36" s="28"/>
+      <c r="L36" s="28"/>
+    </row>
+    <row r="37" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G37" s="28"/>
+      <c r="H37" s="28"/>
+      <c r="K37" s="28"/>
+      <c r="L37" s="28"/>
+    </row>
+    <row r="38" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="K38" s="13"/>
+      <c r="L38" s="13"/>
+    </row>
+    <row r="39" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="K39" s="13"/>
+      <c r="L39" s="13"/>
+    </row>
+    <row r="40" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G40" s="13"/>
+      <c r="H40" s="13"/>
+      <c r="K40" s="13"/>
+      <c r="L40" s="13"/>
+    </row>
+    <row r="41" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G41" s="13"/>
+      <c r="H41" s="13"/>
+      <c r="K41" s="13"/>
+      <c r="L41" s="13"/>
+    </row>
+    <row r="42" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G42" s="13"/>
+      <c r="H42" s="13"/>
+      <c r="K42" s="13"/>
+      <c r="L42" s="13"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{872C15AD-8AB7-49C1-937E-3B0C304F5546}">
+  <dimension ref="D1:L42"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="7" max="8" width="22.5703125" customWidth="1"/>
+    <col min="11" max="12" width="22.5703125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="4:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="2" spans="4:12" ht="47.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G2" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="H2" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="K2" s="2" t="s">
+        <v>119</v>
+      </c>
+      <c r="L2" s="2" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="3" spans="4:12" ht="37.5" x14ac:dyDescent="0.25">
+      <c r="G3" s="36" t="s">
+        <v>163</v>
+      </c>
+      <c r="H3" s="9" t="s">
+        <v>75</v>
+      </c>
+      <c r="K3" s="48" t="s">
+        <v>184</v>
+      </c>
+      <c r="L3" s="9" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="4" spans="4:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G4" s="47" t="s">
+        <v>97</v>
+      </c>
+      <c r="H4" s="9" t="s">
+        <v>75</v>
+      </c>
+      <c r="K4" s="47" t="s">
+        <v>185</v>
+      </c>
+      <c r="L4" s="9" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="5" spans="4:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G5" s="32" t="s">
+        <v>88</v>
+      </c>
+      <c r="H5" s="9" t="s">
+        <v>75</v>
+      </c>
+      <c r="K5" s="47" t="s">
+        <v>186</v>
+      </c>
+      <c r="L5" s="9" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="6" spans="4:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G6" s="47" t="s">
+        <v>99</v>
+      </c>
+      <c r="H6" s="9" t="s">
+        <v>75</v>
+      </c>
+      <c r="K6" s="32" t="s">
+        <v>105</v>
+      </c>
+      <c r="L6" s="9" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="7" spans="4:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G7" s="26" t="s">
+        <v>111</v>
+      </c>
+      <c r="H7" s="9" t="s">
+        <v>75</v>
+      </c>
+      <c r="K7" s="32" t="s">
+        <v>113</v>
+      </c>
+      <c r="L7" s="9" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="8" spans="4:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G8" s="26" t="s">
+        <v>93</v>
+      </c>
+      <c r="H8" s="9" t="s">
+        <v>75</v>
+      </c>
+      <c r="K8" s="32" t="s">
+        <v>94</v>
+      </c>
+      <c r="L8" s="9" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="9" spans="4:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G9" s="26" t="s">
+        <v>82</v>
+      </c>
+      <c r="H9" s="9" t="s">
+        <v>81</v>
+      </c>
+      <c r="K9" s="26" t="s">
+        <v>100</v>
+      </c>
+      <c r="L9" s="9" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="10" spans="4:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G10" s="26" t="s">
+        <v>183</v>
+      </c>
+      <c r="H10" s="9" t="s">
+        <v>81</v>
+      </c>
+      <c r="K10" s="26" t="s">
+        <v>112</v>
+      </c>
+      <c r="L10" s="9" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="11" spans="4:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="D11" s="43"/>
+      <c r="G11" s="14" t="s">
+        <v>179</v>
+      </c>
+      <c r="H11" s="9" t="s">
+        <v>75</v>
+      </c>
+      <c r="K11" s="26" t="s">
+        <v>95</v>
+      </c>
+      <c r="L11" s="9" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="12" spans="4:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G12" s="26" t="s">
+        <v>162</v>
+      </c>
+      <c r="H12" s="9" t="s">
+        <v>75</v>
+      </c>
+      <c r="K12" s="26" t="s">
+        <v>102</v>
+      </c>
+      <c r="L12" s="9" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="13" spans="4:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G13" s="26" t="s">
+        <v>161</v>
+      </c>
+      <c r="H13" s="9" t="s">
+        <v>75</v>
+      </c>
+      <c r="K13" s="26" t="s">
+        <v>106</v>
+      </c>
+      <c r="L13" s="9" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="14" spans="4:12" ht="37.5" x14ac:dyDescent="0.25">
+      <c r="G14" s="10" t="s">
+        <v>181</v>
+      </c>
+      <c r="H14" s="9" t="s">
+        <v>75</v>
+      </c>
+      <c r="K14" s="26" t="s">
+        <v>110</v>
+      </c>
+      <c r="L14" s="9" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="15" spans="4:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G15" s="26" t="s">
+        <v>164</v>
+      </c>
+      <c r="H15" s="9" t="s">
+        <v>81</v>
+      </c>
+      <c r="K15" s="26" t="s">
+        <v>108</v>
+      </c>
+      <c r="L15" s="9" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="16" spans="4:12" ht="37.5" x14ac:dyDescent="0.25">
+      <c r="G16" s="20" t="s">
+        <v>180</v>
+      </c>
+      <c r="H16" s="9" t="s">
+        <v>81</v>
+      </c>
+      <c r="K16" s="26" t="s">
+        <v>85</v>
+      </c>
+      <c r="L16" s="9" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="17" spans="7:12" ht="37.5" x14ac:dyDescent="0.25">
+      <c r="G17" s="20" t="s">
+        <v>189</v>
+      </c>
+      <c r="H17" s="9" t="s">
+        <v>81</v>
+      </c>
+      <c r="K17" s="26" t="s">
+        <v>98</v>
+      </c>
+      <c r="L17" s="9" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="18" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G18" s="21" t="s">
+        <v>165</v>
+      </c>
+      <c r="H18" s="17" t="s">
+        <v>81</v>
+      </c>
+      <c r="K18" s="26" t="s">
+        <v>115</v>
+      </c>
+      <c r="L18" s="9" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="19" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G19" s="16"/>
+      <c r="H19" s="16"/>
+      <c r="K19" s="44" t="s">
+        <v>187</v>
+      </c>
+      <c r="L19" s="9" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="20" spans="7:12" ht="37.5" x14ac:dyDescent="0.25">
+      <c r="G20" s="28"/>
+      <c r="H20" s="28"/>
+      <c r="K20" s="19" t="s">
+        <v>188</v>
+      </c>
+      <c r="L20" s="17" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="21" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G21" s="28"/>
+      <c r="H21" s="28"/>
+      <c r="K21" s="16"/>
+      <c r="L21" s="16"/>
+    </row>
+    <row r="22" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G22" s="28"/>
+      <c r="H22" s="28"/>
+      <c r="K22" s="28"/>
+      <c r="L22" s="28"/>
+    </row>
+    <row r="23" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G23" s="28"/>
+      <c r="H23" s="28"/>
+      <c r="K23" s="28"/>
+      <c r="L23" s="28"/>
+    </row>
+    <row r="24" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G24" s="28"/>
+      <c r="H24" s="28"/>
+      <c r="K24" s="28"/>
+      <c r="L24" s="28"/>
+    </row>
+    <row r="25" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G25" s="28"/>
+      <c r="H25" s="28"/>
+      <c r="K25" s="28"/>
+      <c r="L25" s="28"/>
+    </row>
+    <row r="26" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G26" s="28"/>
+      <c r="H26" s="28"/>
+      <c r="K26" s="28"/>
+      <c r="L26" s="28"/>
+    </row>
+    <row r="27" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G27" s="28"/>
+      <c r="H27" s="28"/>
+      <c r="K27" s="28"/>
+      <c r="L27" s="28"/>
+    </row>
+    <row r="28" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G28" s="28"/>
+      <c r="H28" s="28"/>
+      <c r="K28" s="28"/>
+      <c r="L28" s="28"/>
+    </row>
+    <row r="29" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G29" s="28"/>
+      <c r="H29" s="28"/>
+      <c r="K29" s="28"/>
+      <c r="L29" s="28"/>
+    </row>
+    <row r="30" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G30" s="28"/>
+      <c r="H30" s="28"/>
+      <c r="K30" s="28"/>
+      <c r="L30" s="28"/>
+    </row>
+    <row r="31" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G31" s="28"/>
+      <c r="H31" s="28"/>
+      <c r="K31" s="28"/>
+      <c r="L31" s="28"/>
+    </row>
+    <row r="32" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G32" s="28"/>
+      <c r="H32" s="28"/>
+      <c r="K32" s="28"/>
+      <c r="L32" s="28"/>
+    </row>
+    <row r="33" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G33" s="28"/>
+      <c r="H33" s="28"/>
+      <c r="K33" s="28"/>
+      <c r="L33" s="28"/>
+    </row>
+    <row r="34" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G34" s="28"/>
+      <c r="H34" s="28"/>
+      <c r="K34" s="28"/>
+      <c r="L34" s="28"/>
+    </row>
+    <row r="35" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G35" s="28"/>
+      <c r="H35" s="28"/>
+      <c r="K35" s="28"/>
+      <c r="L35" s="28"/>
+    </row>
+    <row r="36" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G36" s="28"/>
+      <c r="H36" s="28"/>
+      <c r="K36" s="28"/>
+      <c r="L36" s="28"/>
+    </row>
+    <row r="37" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G37" s="28"/>
+      <c r="H37" s="28"/>
+      <c r="K37" s="28"/>
+      <c r="L37" s="28"/>
+    </row>
+    <row r="38" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="K38" s="13"/>
+      <c r="L38" s="13"/>
+    </row>
+    <row r="39" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="K39" s="13"/>
+      <c r="L39" s="13"/>
+    </row>
+    <row r="40" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G40" s="13"/>
+      <c r="H40" s="13"/>
+      <c r="K40" s="13"/>
+      <c r="L40" s="13"/>
+    </row>
+    <row r="41" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G41" s="13"/>
+      <c r="H41" s="13"/>
+      <c r="K41" s="13"/>
+      <c r="L41" s="13"/>
+    </row>
+    <row r="42" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G42" s="13"/>
+      <c r="H42" s="13"/>
+      <c r="K42" s="13"/>
+      <c r="L42" s="13"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
+</worksheet>
 </file>